--- a/Data/Excel/skill_modifier.xlsx
+++ b/Data/Excel/skill_modifier.xlsx
@@ -162,31 +162,31 @@
     <t>Frost Slow</t>
   </si>
   <si>
-    <t>Effect/FrostSlowLoop</t>
+    <t>Assets/Arts/Effects/IceHitEffect.prefab</t>
   </si>
   <si>
     <t>Ice Freeze Slow</t>
   </si>
   <si>
-    <t>Effect/IceFreeze</t>
+    <t>Assets/Arts/Effects/IceHitEffect.prefab</t>
   </si>
   <si>
     <t>Attack Speed Aura Buff</t>
   </si>
   <si>
-    <t>Effect/AuraAttackSpeed</t>
+    <t>Assets/Arts/Effects/IceHitEffect.prefab</t>
   </si>
   <si>
     <t>Poison Dot</t>
   </si>
   <si>
-    <t>Effect/PoisonLoop</t>
+    <t>Assets/Arts/Effects/IceHitEffect.prefab</t>
   </si>
   <si>
     <t>Stun</t>
   </si>
   <si>
-    <t>Effect/StunLoop</t>
+    <t>Assets/Arts/Effects/IceHitEffect.prefab</t>
   </si>
 </sst>
 </file>

--- a/Data/Excel/skill_modifier.xlsx
+++ b/Data/Excel/skill_modifier.xlsx
@@ -715,7 +715,7 @@
     </row>
     <row r="5" spans="1:21" ht="15" customHeight="1">
       <c r="B5" s="5">
-        <v>3001</v>
+        <v>50500001</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>44</v>
@@ -775,7 +775,7 @@
     </row>
     <row r="6" spans="1:21" ht="15" customHeight="1">
       <c r="B6" s="5">
-        <v>3002</v>
+        <v>50500002</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>46</v>
@@ -835,7 +835,7 @@
     </row>
     <row r="7" spans="1:21" ht="15" customHeight="1">
       <c r="B7" s="5">
-        <v>3003</v>
+        <v>50500003</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>48</v>
@@ -895,7 +895,7 @@
     </row>
     <row r="8" spans="1:21" ht="15" customHeight="1">
       <c r="B8" s="5">
-        <v>3004</v>
+        <v>50500004</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>50</v>
@@ -940,7 +940,7 @@
         <v>0</v>
       </c>
       <c r="Q8" s="2">
-        <v>2001</v>
+        <v>50201001</v>
       </c>
       <c r="R8" s="2">
         <v>0</v>
@@ -955,7 +955,7 @@
     </row>
     <row r="9" spans="1:21" ht="15" customHeight="1">
       <c r="B9" s="5">
-        <v>3005</v>
+        <v>50500005</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>52</v>
